--- a/pandemic-loss-modeling/exceedance_results/bernstein_outlier.xlsx
+++ b/pandemic-loss-modeling/exceedance_results/bernstein_outlier.xlsx
@@ -393,7 +393,7 @@
         <v>0.001</v>
       </c>
       <c r="B2">
-        <v>0.9966841825751976</v>
+        <v>0.9935104121243109</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>0.002</v>
       </c>
       <c r="B3">
-        <v>0.9933893979367583</v>
+        <v>0.9871026128131208</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>7.2</v>
       </c>
       <c r="B4">
-        <v>0.03294983585893488</v>
+        <v>0.01813602799646403</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>28</v>
       </c>
       <c r="B5">
-        <v>0.007788195109246173</v>
+        <v>0.004443775412334577</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>45</v>
       </c>
       <c r="B6">
-        <v>0.004669243827310834</v>
+        <v>0.002708681512121208</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -433,7 +433,7 @@
         <v>86</v>
       </c>
       <c r="B7">
-        <v>0.002316015071135645</v>
+        <v>0.001376261558283611</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -441,7 +441,7 @@
         <v>150</v>
       </c>
       <c r="B8">
-        <v>0.00126640144909073</v>
+        <v>0.0007688440662844799</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -449,7 +449,7 @@
         <v>200</v>
       </c>
       <c r="B9">
-        <v>0.0009265159999182385</v>
+        <v>0.0005688605650998471</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -457,7 +457,7 @@
         <v>220</v>
       </c>
       <c r="B10">
-        <v>0.0008353602863119923</v>
+        <v>0.0005148176373850862</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -465,7 +465,7 @@
         <v>250</v>
       </c>
       <c r="B11">
-        <v>0.0007270032859874662</v>
+        <v>0.0004503010426544003</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -473,7 +473,7 @@
         <v>280</v>
       </c>
       <c r="B12">
-        <v>0.0006427419767627664</v>
+        <v>0.0003998955314019599</v>
       </c>
     </row>
   </sheetData>

--- a/pandemic-loss-modeling/exceedance_results/bernstein_outlier.xlsx
+++ b/pandemic-loss-modeling/exceedance_results/bernstein_outlier.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -390,89 +390,81 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>0.001</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.9935104121243109</v>
+        <v>0.9386092439710866</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>0.002</v>
+        <v>7.2</v>
       </c>
       <c r="B3">
-        <v>0.9871026128131208</v>
+        <v>0.01813602799646403</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="B4">
-        <v>0.01813602799646403</v>
+        <v>0.004443775412334577</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="B5">
-        <v>0.004443775412334577</v>
+        <v>0.002708681512121208</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="B6">
-        <v>0.002708681512121208</v>
+        <v>0.001376261558283611</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="B7">
-        <v>0.001376261558283611</v>
+        <v>0.0007688440662844799</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="B8">
-        <v>0.0007688440662844799</v>
+        <v>0.0005688605650998471</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="B9">
-        <v>0.0005688605650998471</v>
+        <v>0.0005148176373850862</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="B10">
-        <v>0.0005148176373850862</v>
+        <v>0.0004503010426544003</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="B11">
-        <v>0.0004503010426544003</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
-        <v>280</v>
-      </c>
-      <c r="B12">
         <v>0.0003998955314019599</v>
       </c>
     </row>

--- a/pandemic-loss-modeling/exceedance_results/bernstein_outlier.xlsx
+++ b/pandemic-loss-modeling/exceedance_results/bernstein_outlier.xlsx
@@ -393,7 +393,7 @@
         <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.9386092439710866</v>
+        <v>0.8592506534996551</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>7.2</v>
       </c>
       <c r="B3">
-        <v>0.01813602799646403</v>
+        <v>0.0077908408328232</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>28</v>
       </c>
       <c r="B4">
-        <v>0.004443775412334577</v>
+        <v>0.001960878915745123</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>45</v>
       </c>
       <c r="B5">
-        <v>0.002708681512121208</v>
+        <v>0.001209276207291931</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>86</v>
       </c>
       <c r="B6">
-        <v>0.001376261558283611</v>
+        <v>0.0006247981730294086</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -433,7 +433,7 @@
         <v>150</v>
       </c>
       <c r="B7">
-        <v>0.0007688440662844799</v>
+        <v>0.0003542492586713024</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -441,7 +441,7 @@
         <v>200</v>
       </c>
       <c r="B8">
-        <v>0.0005688605650998471</v>
+        <v>0.0002641456252684383</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -449,7 +449,7 @@
         <v>220</v>
       </c>
       <c r="B9">
-        <v>0.0005148176373850862</v>
+        <v>0.0002396684698001436</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -457,7 +457,7 @@
         <v>250</v>
       </c>
       <c r="B10">
-        <v>0.0004503010426544003</v>
+        <v>0.0002103610768777687</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -465,7 +465,7 @@
         <v>280</v>
       </c>
       <c r="B11">
-        <v>0.0003998955314019599</v>
+        <v>0.0001873896772814921</v>
       </c>
     </row>
   </sheetData>

--- a/pandemic-loss-modeling/exceedance_results/bernstein_outlier.xlsx
+++ b/pandemic-loss-modeling/exceedance_results/bernstein_outlier.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -398,73 +398,249 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>7.2</v>
+        <v>0.04</v>
       </c>
       <c r="B3">
-        <v>0.0077908408328232</v>
+        <v>0.6032034702734694</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>28</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="B4">
-        <v>0.001960878915745123</v>
+        <v>0.4640674134023541</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>45</v>
+        <v>0.08</v>
       </c>
       <c r="B5">
-        <v>0.001209276207291931</v>
+        <v>0.4308326862292308</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>86</v>
+        <v>0.1</v>
       </c>
       <c r="B6">
-        <v>0.0006247981730294086</v>
+        <v>0.3767545388576576</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>150</v>
+        <v>0.4</v>
       </c>
       <c r="B7">
-        <v>0.0003542492586713024</v>
+        <v>0.1295013634126901</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>200</v>
+        <v>0.7</v>
       </c>
       <c r="B8">
-        <v>0.0002641456252684383</v>
+        <v>0.07773890448316352</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>220</v>
+        <v>1</v>
       </c>
       <c r="B9">
-        <v>0.0002396684698001436</v>
+        <v>0.05540720079531727</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>250</v>
+        <v>4</v>
       </c>
       <c r="B10">
-        <v>0.0002103610768777687</v>
+        <v>0.01409539460612852</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>0.008016077916874262</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>8</v>
+      </c>
+      <c r="B12">
+        <v>0.007002700882197732</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>0.005585300632255731</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <v>0.003700379340189667</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>20</v>
+      </c>
+      <c r="B15">
+        <v>0.002761811013431374</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>28</v>
+      </c>
+      <c r="B16">
+        <v>0.001960878915745123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>40</v>
+      </c>
+      <c r="B17">
+        <v>0.00136349861052292</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>45</v>
+      </c>
+      <c r="B18">
+        <v>0.001209276207291931</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>70</v>
+      </c>
+      <c r="B19">
+        <v>0.0007707397145865978</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>86</v>
+      </c>
+      <c r="B20">
+        <v>0.0006247981730294086</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>100</v>
+      </c>
+      <c r="B21">
+        <v>0.0005357156333790926</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>120</v>
+      </c>
+      <c r="B22">
+        <v>0.0004448038741564079</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>150</v>
+      </c>
+      <c r="B23">
+        <v>0.0003542492586713024</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>170</v>
+      </c>
+      <c r="B24">
+        <v>0.0003117838253922988</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>190</v>
+      </c>
+      <c r="B25">
+        <v>0.0002783372167673175</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>200</v>
+      </c>
+      <c r="B26">
+        <v>0.0002641456252684383</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>220</v>
+      </c>
+      <c r="B27">
+        <v>0.0002396684698001436</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>230</v>
+      </c>
+      <c r="B28">
+        <v>0.0002290412261857218</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>240</v>
+      </c>
+      <c r="B29">
+        <v>0.00021930808039454</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>250</v>
+      </c>
+      <c r="B30">
+        <v>0.0002103610768777687</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>260</v>
+      </c>
+      <c r="B31">
+        <v>0.0002021089432959424</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>270</v>
+      </c>
+      <c r="B32">
+        <v>0.0001944739902587565</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
         <v>280</v>
       </c>
-      <c r="B11">
+      <c r="B33">
         <v>0.0001873896772814921</v>
       </c>
     </row>
